--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:09</t>
+    <t xml:space="preserve">2026-09-09 23:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:03</t>
+    <t xml:space="preserve">2026-09-17 14:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:00</t>
+    <t xml:space="preserve">2026-09-23 12:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:29</t>
+    <t xml:space="preserve">2026-10-02 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:13</t>
+    <t xml:space="preserve">2026-10-05 10:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -883,7 +883,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>650705.12</v>
+        <v>650705.13</v>
       </c>
     </row>
     <row r="21">
@@ -917,7 +917,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>642748.62</v>
+        <v>642748.63</v>
       </c>
     </row>
     <row r="23">
@@ -968,7 +968,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>629482.12</v>
+        <v>629482.13</v>
       </c>
     </row>
     <row r="26">
@@ -1019,7 +1019,7 @@
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>602530.62</v>
+        <v>602530.63</v>
       </c>
     </row>
     <row r="29">
@@ -1053,7 +1053,7 @@
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>583838.12</v>
+        <v>583838.13</v>
       </c>
     </row>
     <row r="31">
